--- a/laporan_padel_dki_jakarta_2026-09-14.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-14.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,16 +513,16 @@
         <v>48</v>
       </c>
       <c r="D3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp650.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -544,16 +544,16 @@
         <v>104</v>
       </c>
       <c r="D4" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp11.600.000</t>
+          <t>Rp13.600.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -606,16 +606,16 @@
         <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp550.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -637,16 +637,16 @@
         <v>44</v>
       </c>
       <c r="D7" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp376.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>44</v>
       </c>
       <c r="D8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp5.020.000</t>
+          <t>Rp5.295.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>52</v>
       </c>
       <c r="D10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.093.994</t>
+          <t>Rp2.791.992</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>130</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp8.604.500</t>
+          <t>Rp10.584.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1071,16 +1071,16 @@
         <v>115</v>
       </c>
       <c r="D21" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp14.744.000</t>
+          <t>Rp15.393.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>72</v>
       </c>
       <c r="D22" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp2.900.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>104</v>
       </c>
       <c r="D23" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.700.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>52</v>
       </c>
       <c r="D24" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.030.000</t>
+          <t>Rp4.325.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>48</v>
       </c>
       <c r="D32" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.380.000</t>
+          <t>Rp2.300.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>52</v>
       </c>
       <c r="D33" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp1.696.000</t>
+          <t>Rp1.992.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>48</v>
       </c>
       <c r="D34" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp150.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>52</v>
       </c>
       <c r="D35" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp4.295.000</t>
+          <t>Rp3.345.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>44</v>
       </c>
       <c r="D36" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp1.850.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1560,28 +1560,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Padre Padel Duri Kosambi</t>
+          <t>La Chiquita Padel</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="D37" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp420.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp210.000</t>
+          <t>Rp300.000</t>
         </is>
       </c>
     </row>
@@ -1591,28 +1591,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Padeloo</t>
+          <t>Padre Padel Duri Kosambi</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D38" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.956.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp195.000</t>
+          <t>Rp150.000 - Rp210.000</t>
         </is>
       </c>
     </row>
@@ -1622,28 +1622,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CPH Citra Padel House</t>
+          <t>Padeloo</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D39" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp905.000</t>
+          <t>Rp1.956.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rp75.000 - Rp170.000</t>
+          <t>Rp99.000 - Rp195.000</t>
         </is>
       </c>
     </row>
@@ -1653,28 +1653,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vamos Arena Indonesia</t>
+          <t>CPH Citra Padel House</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>130</v>
+        <v>36</v>
       </c>
       <c r="D40" t="n">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp9.050.000</t>
+          <t>Rp1.245.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp400.000</t>
+          <t>Rp75.000 - Rp170.000</t>
         </is>
       </c>
     </row>
@@ -1684,28 +1684,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The Level 9 Padel</t>
+          <t>Vamos Arena Indonesia</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="D41" t="n">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp9.050.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp150.000</t>
+          <t>Rp200.000 - Rp400.000</t>
         </is>
       </c>
     </row>
@@ -1715,28 +1715,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Como Padel Court</t>
+          <t>The Level 9 Padel</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>44</v>
+        <v>143</v>
       </c>
       <c r="D42" t="n">
-        <v>33</v>
+        <v>126</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.099.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp200.000</t>
+          <t>Rp125.000 - Rp150.000</t>
         </is>
       </c>
     </row>
@@ -1746,28 +1746,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>World Padel</t>
+          <t>Como Padel Court</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D43" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp99.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rp50.000 - Rp225.000</t>
+          <t>Rp99.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -1777,28 +1777,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Padelin</t>
+          <t>World Padel</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D44" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp200.000</t>
+          <t>Rp50.000 - Rp225.000</t>
         </is>
       </c>
     </row>
@@ -1808,28 +1808,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nordic Courts</t>
+          <t>Padelin</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="D45" t="n">
         <v>39</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp4.299.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rp77.000 - Rp250.000</t>
+          <t>Rp100.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -1839,28 +1839,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Courtyard Padel Club</t>
+          <t>Nordic Courts</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D46" t="n">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp3.710.000</t>
+          <t>Rp4.549.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rp165.000 - Rp650.000</t>
+          <t>Rp77.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -1870,28 +1870,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Padel On Mars</t>
+          <t>Courtyard Padel Club</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="D47" t="n">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp540.000</t>
+          <t>Rp3.710.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rp115.000 - Rp135.000</t>
+          <t>Rp165.000 - Rp650.000</t>
         </is>
       </c>
     </row>
@@ -1901,28 +1901,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Padel Meruya Airdome</t>
+          <t>Padel On Mars</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="D48" t="n">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp2.194.000</t>
+          <t>Rp540.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Rp349.000 - Rp399.000</t>
+          <t>Rp115.000 - Rp135.000</t>
         </is>
       </c>
     </row>
@@ -1932,28 +1932,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hachi Padel Puri Indah Jakarta</t>
+          <t>Padel Meruya Airdome</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="D49" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp576.000</t>
+          <t>Rp2.992.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Rp288.000</t>
+          <t>Rp349.000 - Rp399.000</t>
         </is>
       </c>
     </row>
@@ -1963,28 +1963,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JC Padel Kedoya</t>
+          <t>Hachi Padel Puri Indah Jakarta</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D50" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp760.000</t>
+          <t>Rp576.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Rp140.000 - Rp380.000</t>
+          <t>Rp288.000</t>
         </is>
       </c>
     </row>
@@ -1994,28 +1994,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tennis Padel Matic Mal Ciputra</t>
+          <t>JC Padel Kedoya</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="D51" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp1.920.000</t>
+          <t>Rp760.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Rp80.000</t>
+          <t>Rp140.000 - Rp380.000</t>
         </is>
       </c>
     </row>
@@ -2025,28 +2025,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Paddle Padel</t>
+          <t>Tennis Padel Matic Mal Ciputra</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="D52" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp2.080.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp200.000</t>
+          <t>Rp80.000</t>
         </is>
       </c>
     </row>
@@ -2056,28 +2056,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Roots Padel House</t>
+          <t>Paddle Padel</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="D53" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Rp149.000 - Rp200.000</t>
+          <t>Rp150.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -2087,28 +2087,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Coco Padel Court Jakarta</t>
+          <t>Roots Padel House</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="D54" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>15.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp915.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Rp115.000 - Rp200.000</t>
+          <t>Rp149.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -2118,28 +2118,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Zplay Padel</t>
+          <t>Coco Padel Court Jakarta</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D55" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp670.000</t>
+          <t>Rp915.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Rp65.000 - Rp175.000</t>
+          <t>Rp115.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -2149,28 +2149,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PPC - Puri Padel Club</t>
+          <t>Zplay Padel</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D56" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp750.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rp225.000 - Rp275.000</t>
+          <t>Rp65.000 - Rp175.000</t>
         </is>
       </c>
     </row>
@@ -2180,28 +2180,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Donkey Padel</t>
+          <t>PPC - Puri Padel Club</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D57" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp496.000</t>
+          <t>Rp1.550.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Rp99.000 - Rp149.000</t>
+          <t>Rp225.000 - Rp275.000</t>
         </is>
       </c>
     </row>
@@ -2211,28 +2211,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Sunrise Padel - Sunrise Garden</t>
+          <t>Donkey Padel</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D58" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp1.680.000</t>
+          <t>Rp794.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rp120.000</t>
+          <t>Rp99.000 - Rp149.000</t>
         </is>
       </c>
     </row>
@@ -2242,28 +2242,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ace Padel Club (APC) - Jalan Panjang Kedoya</t>
+          <t>Sunrise Padel - Sunrise Garden</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D59" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp6.760.000</t>
+          <t>Rp1.680.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp300.000</t>
+          <t>Rp120.000</t>
         </is>
       </c>
     </row>
@@ -2273,28 +2273,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Padel Quarter</t>
+          <t>Ace Padel Club (APC) - Jalan Panjang Kedoya</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="D60" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp710.000</t>
+          <t>Rp7.060.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rp80.000 - Rp380.000</t>
+          <t>Rp100.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -2304,28 +2304,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Go 2 Padel</t>
+          <t>Padel Quarter</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="D61" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp60.000</t>
+          <t>Rp2.110.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rp60.000 - Rp150.000</t>
+          <t>Rp80.000 - Rp360.000</t>
         </is>
       </c>
     </row>
@@ -2335,28 +2335,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>YOLO Padel and Lifestyle Slipi</t>
+          <t>Go 2 Padel</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D62" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp1.500.000</t>
+          <t>Rp660.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Rp300.000 - Rp375.000</t>
+          <t>Rp60.000 - Rp150.000</t>
         </is>
       </c>
     </row>
@@ -2366,28 +2366,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>KALMA Social Club - Jl. Panjang, Kedoya</t>
+          <t>YOLO Padel and Lifestyle Slipi</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="D63" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp5.185.000</t>
+          <t>Rp1.500.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp399.000</t>
+          <t>Rp300.000 - Rp375.000</t>
         </is>
       </c>
     </row>
@@ -2397,28 +2397,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Padel V</t>
+          <t>KALMA Social Club - Jl. Panjang, Kedoya</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="D64" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp1.040.000</t>
+          <t>Rp5.185.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rp160.000 - Rp260.000</t>
+          <t>Rp150.000 - Rp399.000</t>
         </is>
       </c>
     </row>
@@ -2428,28 +2428,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Country Club | Padel &amp; Lounge</t>
+          <t>Padel V</t>
         </is>
       </c>
       <c r="C65" t="n">
         <v>24</v>
       </c>
       <c r="D65" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp1.040.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp250.000</t>
+          <t>Rp160.000 - Rp260.000</t>
         </is>
       </c>
     </row>
@@ -2459,28 +2459,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Social Field</t>
+          <t>Country Club | Padel &amp; Lounge</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>136</v>
+        <v>24</v>
       </c>
       <c r="D66" t="n">
-        <v>130</v>
+        <v>19</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp1.594.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Rp99.500 - Rp299.000</t>
+          <t>Rp200.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -2490,28 +2490,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PIPC - Play In Padel Collective - Srengseng</t>
+          <t>Social Field</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="D67" t="n">
-        <v>57</v>
+        <v>124</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.188.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp250.000</t>
+          <t>Rp99.500 - Rp299.000</t>
         </is>
       </c>
     </row>
@@ -2521,28 +2521,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>United Padel Club</t>
+          <t>PIPC - Play In Padel Collective - Srengseng</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="D68" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp960.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Rp120.000 - Rp180.000</t>
+          <t>Rp100.000 - Rp250.000</t>
         </is>
       </c>
     </row>
@@ -2552,28 +2552,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Powerhouse Padel AZURE Taman Surya</t>
+          <t>United Padel Club</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="D69" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp980.000</t>
+          <t>Rp1.680.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Rp75.000 - Rp170.000</t>
+          <t>Rp120.000 - Rp180.000</t>
         </is>
       </c>
     </row>
@@ -2583,28 +2583,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>OLA PADEL CLUB</t>
+          <t>Powerhouse Padel AZURE Taman Surya</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="D70" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp5.670.000</t>
+          <t>Rp980.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp260.000</t>
+          <t>Rp75.000 - Rp170.000</t>
         </is>
       </c>
     </row>
@@ -2614,28 +2614,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MMT Padel</t>
+          <t>OLA PADEL CLUB</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D71" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp3.420.000</t>
+          <t>Rp5.670.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Rp230.000 - Rp350.000</t>
+          <t>Rp100.000 - Rp260.000</t>
         </is>
       </c>
     </row>
@@ -2645,28 +2645,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Clubhouse Meruya</t>
+          <t>MMT Padel</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="D72" t="n">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Rp2.880.000</t>
+          <t>Rp4.720.000</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Rp160.000</t>
+          <t>Rp230.000 - Rp350.000</t>
         </is>
       </c>
     </row>
@@ -2676,28 +2676,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Angke Padel</t>
+          <t>Clubhouse Meruya</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D73" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp1.950.000</t>
+          <t>Rp3.680.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Rp75.000 - Rp150.000</t>
+          <t>Rp160.000</t>
         </is>
       </c>
     </row>
@@ -2707,28 +2707,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>DAAN MOGOT PADEL COURT</t>
+          <t>Angke Padel</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="D74" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp500.000</t>
+          <t>Rp75.000 - Rp150.000</t>
         </is>
       </c>
     </row>
@@ -2738,28 +2738,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Kaia Padel Reserve</t>
+          <t>DAAN MOGOT PADEL COURT</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D75" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp2.150.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp200.000</t>
+          <t>Rp125.000 - Rp500.000</t>
         </is>
       </c>
     </row>
@@ -2769,28 +2769,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tangkas Padel</t>
+          <t>Kaia Padel Reserve</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="D76" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp2.150.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp300.000</t>
+          <t>Rp150.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -2800,28 +2800,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cosmo Padel</t>
+          <t>Tangkas Padel</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D77" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Rp128.000 - Rp275.000</t>
+          <t>Rp150.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -2831,14 +2831,14 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MAISON de PADEL</t>
+          <t>Cosmo Padel</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D78" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Rp275.000 - Rp450.000</t>
+          <t>Rp128.000 - Rp275.000</t>
         </is>
       </c>
     </row>
@@ -2862,14 +2862,14 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Di Atas Social Club - Lippo Mall Puri</t>
+          <t>MAISON de PADEL</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>99</v>
+        <v>11</v>
       </c>
       <c r="D79" t="n">
-        <v>99</v>
+        <v>11</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Rp195.000 - Rp280.000</t>
+          <t>Rp275.000 - Rp450.000</t>
         </is>
       </c>
     </row>
@@ -2893,28 +2893,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Commune Courts</t>
+          <t>Di Atas Social Club - Lippo Mall Puri</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="D80" t="n">
-        <v>49</v>
+        <v>99</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp300.000</t>
+          <t>Rp195.000 - Rp280.000</t>
         </is>
       </c>
     </row>
@@ -2924,28 +2924,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EL WILLY PADEL</t>
+          <t>Commune Courts</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="D81" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp4.130.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rp250.000 - Rp380.000</t>
+          <t>Rp100.000 - Rp300.000</t>
         </is>
       </c>
     </row>
@@ -2955,28 +2955,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Dash Padel House</t>
+          <t>EL WILLY PADEL</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="D82" t="n">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp3.187.000</t>
+          <t>Rp4.130.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Rp100.000 - Rp249.000</t>
+          <t>Rp250.000 - Rp380.000</t>
         </is>
       </c>
     </row>
@@ -2986,28 +2986,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Citra Padel Club</t>
+          <t>Dash Padel House</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="D83" t="n">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp4.250.000</t>
+          <t>Rp3.436.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rp70.000 - Rp225.000</t>
+          <t>Rp100.000 - Rp249.000</t>
         </is>
       </c>
     </row>
@@ -3017,28 +3017,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Malta Padel Club</t>
+          <t>Citra Padel Club</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>65</v>
+        <v>96</v>
       </c>
       <c r="D84" t="n">
-        <v>55</v>
+        <v>71</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp4.475.000</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp200.000</t>
+          <t>Rp70.000 - Rp225.000</t>
         </is>
       </c>
     </row>
@@ -3048,28 +3048,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>De Luz Padel</t>
+          <t>Malta Padel Club</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D85" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Rp1.455.000</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Rp80.000 - Rp180.000</t>
+          <t>Rp150.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -3079,28 +3079,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Nice Padel</t>
+          <t>De Luz Padel</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="D86" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp396.000</t>
+          <t>Rp2.795.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rp99.000</t>
+          <t>Rp80.000 - Rp180.000</t>
         </is>
       </c>
     </row>
@@ -3110,28 +3110,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Golcindo Padel Club</t>
+          <t>Nice Padel</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D87" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp773.000</t>
+          <t>Rp396.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Rp59.000 - Rp149.000</t>
+          <t>Rp99.000</t>
         </is>
       </c>
     </row>
@@ -3141,28 +3141,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Mono House</t>
+          <t>Golcindo Padel Club</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D88" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp773.000</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp225.000</t>
+          <t>Rp59.000 - Rp149.000</t>
         </is>
       </c>
     </row>
@@ -3172,28 +3172,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Seven Stars Arena</t>
+          <t>Mono House</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="D89" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp500.000</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Rp125.000 - Rp220.000</t>
+          <t>Rp125.000 - Rp225.000</t>
         </is>
       </c>
     </row>
@@ -3203,28 +3203,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Deuce Arena</t>
+          <t>Seven Stars Arena</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="D90" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp1.648.000</t>
+          <t>Rp440.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Rp39.000 - Rp250.000</t>
+          <t>Rp125.000 - Rp220.000</t>
         </is>
       </c>
     </row>
@@ -3234,26 +3234,57 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
+          <t>Deuce Arena</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>84</v>
+      </c>
+      <c r="D91" t="n">
+        <v>48</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Rp2.048.000</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Rp39.000 - Rp250.000</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
           <t>SERA COMMUNITY CLUB</t>
         </is>
       </c>
-      <c r="C91" t="n">
+      <c r="C92" t="n">
         <v>18</v>
       </c>
-      <c r="D91" t="n">
-        <v>17</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>5.6%</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Rp400.000</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
+      <c r="D92" t="n">
+        <v>16</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>11.1%</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Rp800.000</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
         <is>
           <t>Rp165.000 - Rp400.000</t>
         </is>
@@ -3385,16 +3416,16 @@
         <v>72</v>
       </c>
       <c r="D4" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3416,16 +3447,16 @@
         <v>78</v>
       </c>
       <c r="D5" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.500.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3447,16 +3478,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3850,16 +3881,16 @@
         <v>39</v>
       </c>
       <c r="D19" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.925.000</t>
+          <t>Rp5.825.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4067,16 +4098,16 @@
         <v>39</v>
       </c>
       <c r="D26" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp770.000</t>
+          <t>Rp1.540.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4098,16 +4129,16 @@
         <v>12</v>
       </c>
       <c r="D27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp80.000</t>
+          <t>Rp200.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4160,16 +4191,16 @@
         <v>120</v>
       </c>
       <c r="D29" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp6.875.000</t>
+          <t>Rp7.375.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4253,16 +4284,16 @@
         <v>52</v>
       </c>
       <c r="D32" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp848.000</t>
+          <t>Rp1.648.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4439,16 +4470,16 @@
         <v>115</v>
       </c>
       <c r="D38" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp10.300.000</t>
+          <t>Rp10.400.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4501,16 +4532,16 @@
         <v>30</v>
       </c>
       <c r="D40" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.125.000</t>
+          <t>Rp3.375.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4532,16 +4563,16 @@
         <v>22</v>
       </c>
       <c r="D41" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4594,16 +4625,16 @@
         <v>40</v>
       </c>
       <c r="D43" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4811,16 +4842,16 @@
         <v>22</v>
       </c>
       <c r="D50" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp2.656.000</t>
+          <t>Rp2.324.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4842,16 +4873,16 @@
         <v>60</v>
       </c>
       <c r="D51" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp500.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4904,16 +4935,16 @@
         <v>52</v>
       </c>
       <c r="D53" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp5.148.000</t>
+          <t>Rp4.752.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5028,16 +5059,16 @@
         <v>27</v>
       </c>
       <c r="D57" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp3.385.000</t>
+          <t>Rp4.705.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5090,16 +5121,16 @@
         <v>60</v>
       </c>
       <c r="D59" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp71.000</t>
+          <t>Rp124.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5135,7 +5166,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Rp150.000 - Rp175.000</t>
+          <t>Rp140.000 - Rp175.000</t>
         </is>
       </c>
     </row>
@@ -5183,16 +5214,16 @@
         <v>22</v>
       </c>
       <c r="D62" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp510.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5276,16 +5307,16 @@
         <v>48</v>
       </c>
       <c r="D65" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp7.800.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5338,16 +5369,16 @@
         <v>72</v>
       </c>
       <c r="D67" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp1.188.000</t>
+          <t>Rp1.485.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5544,16 +5575,16 @@
         <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp450.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5668,16 +5699,16 @@
         <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp980.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5730,16 +5761,16 @@
         <v>154</v>
       </c>
       <c r="D8" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp29.250.000</t>
+          <t>Rp30.700.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5761,16 +5792,16 @@
         <v>39</v>
       </c>
       <c r="D9" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.950.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -5854,16 +5885,16 @@
         <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp4.690.000</t>
+          <t>Rp5.025.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5916,16 +5947,16 @@
         <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp680.000</t>
+          <t>Rp980.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5947,16 +5978,16 @@
         <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.310.000</t>
+          <t>Rp1.740.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6071,16 +6102,16 @@
         <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp228.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6111,7 +6142,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp3.690.000</t>
+          <t>Rp4.090.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6184,16 +6215,16 @@
         <v>150</v>
       </c>
       <c r="D2" t="n">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp7.820.000</t>
+          <t>Rp8.380.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6215,16 +6246,16 @@
         <v>61</v>
       </c>
       <c r="D3" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp6.300.000</t>
+          <t>Rp6.800.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6277,16 +6308,16 @@
         <v>52</v>
       </c>
       <c r="D5" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp398.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6317,7 +6348,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp12.005.000</t>
+          <t>Rp11.905.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6370,16 +6401,16 @@
         <v>39</v>
       </c>
       <c r="D8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6401,16 +6432,16 @@
         <v>72</v>
       </c>
       <c r="D9" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp6.252.000</t>
+          <t>Rp7.631.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6463,16 +6494,16 @@
         <v>156</v>
       </c>
       <c r="D11" t="n">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp9.784.000</t>
+          <t>Rp11.344.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6556,16 +6587,16 @@
         <v>104</v>
       </c>
       <c r="D14" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>21.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp4.700.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6618,16 +6649,16 @@
         <v>78</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp3.850.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6649,16 +6680,16 @@
         <v>104</v>
       </c>
       <c r="D17" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>2.9%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp200.000</t>
+          <t>Rp850.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6680,16 +6711,16 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.500.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6711,16 +6742,16 @@
         <v>27</v>
       </c>
       <c r="D19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.297.000</t>
+          <t>Rp3.835.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6742,16 +6773,16 @@
         <v>36</v>
       </c>
       <c r="D20" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp396.000</t>
+          <t>Rp693.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6773,16 +6804,16 @@
         <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp14.900.000</t>
+          <t>Rp16.200.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6804,16 +6835,16 @@
         <v>52</v>
       </c>
       <c r="D22" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp6.500.000</t>
+          <t>Rp6.150.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -6835,16 +6866,16 @@
         <v>84</v>
       </c>
       <c r="D23" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.903.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -6897,16 +6928,16 @@
         <v>78</v>
       </c>
       <c r="D25" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.025.000</t>
+          <t>Rp3.575.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -6990,16 +7021,16 @@
         <v>48</v>
       </c>
       <c r="D28" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp2.415.000</t>
+          <t>Rp3.105.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7021,16 +7052,16 @@
         <v>48</v>
       </c>
       <c r="D29" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp6.350.000</t>
+          <t>Rp6.570.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7083,16 +7114,16 @@
         <v>52</v>
       </c>
       <c r="D31" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.445.000</t>
+          <t>Rp2.340.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7145,16 +7176,16 @@
         <v>143</v>
       </c>
       <c r="D33" t="n">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp10.200.000</t>
+          <t>Rp12.400.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7238,16 +7269,16 @@
         <v>60</v>
       </c>
       <c r="D36" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.475.000</t>
+          <t>Rp4.350.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7269,16 +7300,16 @@
         <v>24</v>
       </c>
       <c r="D37" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp576.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7331,16 +7362,16 @@
         <v>105</v>
       </c>
       <c r="D39" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp14.525.000</t>
+          <t>Rp14.825.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7362,16 +7393,16 @@
         <v>96</v>
       </c>
       <c r="D40" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp8.800.000</t>
+          <t>Rp10.400.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7424,16 +7455,16 @@
         <v>84</v>
       </c>
       <c r="D42" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp5.525.000</t>
+          <t>Rp5.790.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7579,16 +7610,16 @@
         <v>68</v>
       </c>
       <c r="D47" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp7.150.000</t>
+          <t>Rp6.170.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7610,16 +7641,16 @@
         <v>104</v>
       </c>
       <c r="D48" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp760.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7723,16 +7754,16 @@
         <v>52</v>
       </c>
       <c r="D2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp970.000</t>
+          <t>Rp1.320.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -7754,16 +7785,16 @@
         <v>96</v>
       </c>
       <c r="D3" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp4.445.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -7816,16 +7847,16 @@
         <v>63</v>
       </c>
       <c r="D5" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp4.700.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -7878,16 +7909,16 @@
         <v>33</v>
       </c>
       <c r="D7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp1.810.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8095,16 +8126,16 @@
         <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp950.000</t>
+          <t>Rp2.450.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8126,16 +8157,16 @@
         <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp375.000</t>
+          <t>Rp875.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8188,16 +8219,16 @@
         <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp540.000</t>
+          <t>Rp810.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8219,16 +8250,16 @@
         <v>39</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.790.000</t>
+          <t>Rp2.210.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8312,16 +8343,16 @@
         <v>72</v>
       </c>
       <c r="D21" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp15.100.000</t>
+          <t>Rp16.060.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8405,16 +8436,16 @@
         <v>104</v>
       </c>
       <c r="D24" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp3.315.000</t>
+          <t>Rp4.095.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8560,16 +8591,16 @@
         <v>24</v>
       </c>
       <c r="D29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8622,16 +8653,16 @@
         <v>39</v>
       </c>
       <c r="D31" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp1.039.000</t>
+          <t>Rp694.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -8715,16 +8746,16 @@
         <v>26</v>
       </c>
       <c r="D34" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp1.560.000</t>
+          <t>Rp1.755.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -8777,16 +8808,16 @@
         <v>36</v>
       </c>
       <c r="D36" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp370.000</t>
+          <t>Rp740.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -8808,16 +8839,16 @@
         <v>52</v>
       </c>
       <c r="D37" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp694.000</t>
+          <t>Rp892.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -8839,16 +8870,16 @@
         <v>39</v>
       </c>
       <c r="D38" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
